--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92556767531</v>
+        <v>46157.9311812407</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.9311812407</v>
+        <v>46157.93140006329</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93140006329</v>
+        <v>46157.93386704097</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93386704097</v>
+        <v>46157.93698597179</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93698597179</v>
+        <v>46158.28206294352</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28206294352</v>
+        <v>46158.29655476401</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29655476401</v>
+        <v>46158.29810632663</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29810632663</v>
+        <v>46158.33372908274</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33372908274</v>
+        <v>46158.37225731306</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/12_Разнарядки/Разнорядки 2025/Октябрь/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37225731306</v>
+        <v>46158.37276887034</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
